--- a/doc/03.概要设计/数据库表.xlsx
+++ b/doc/03.概要设计/数据库表.xlsx
@@ -43,7 +43,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'favorite'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'favorite'!$A$1:$P$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'viewing_appointment'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'viewing_appointment'!$A$1:$P$17</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'viewing_appointment'!$A$1:$P$18</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'contract'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'contract'!$A$1:$P$22</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'lease_order'!$4:$4</definedName>
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -891,12 +891,12 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>house_id，appointment_time</t>
+          <t>active_slot</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>FR-17 预约看房；UNIQUE(house_id, appointment_time) 防同时段重复预约；landlord_id 为查询冗余列（源于房源）</t>
+          <t>FR-17 预约看房；UNIQUE(active_slot) 防同时段重复预约——仅待确认/已确认持有占位键，终态置 NULL 释放时段；landlord_id 为查询冗余列（源于房源）</t>
         </is>
       </c>
     </row>
@@ -10973,7 +10973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -11041,7 +11041,7 @@
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
-          <t>FR-17 预约看房；UNIQUE(house_id, appointment_time) 防同时段重复预约；landlord_id 为查询冗余列（源于房源）</t>
+          <t>FR-17 预约看房；UNIQUE(active_slot) 防同时段重复预约——仅待确认/已确认持有占位键，终态置 NULL 释放时段；landlord_id 为查询冗余列（源于房源）</t>
         </is>
       </c>
     </row>
@@ -11183,7 +11183,7 @@
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>FK fk_appt_house → house.id；UNIQUE uk_house_time</t>
+          <t>FK fk_appt_house → house.id</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
@@ -11316,11 +11316,7 @@
         </is>
       </c>
       <c r="F9" s="2" t="n"/>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>UNIQUE uk_house_time</t>
-        </is>
-      </c>
+      <c r="G9" s="4" t="n"/>
       <c r="H9" s="4" t="inlineStr">
         <is>
           <t>预约时段（起点）</t>
@@ -11399,31 +11395,39 @@
         </is>
       </c>
       <c r="C11" s="2" t="n">
-        <v>200</v>
+        <v>64</v>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>reject_reason</t>
+          <t>active_slot</t>
         </is>
       </c>
       <c r="E11" s="2" t="n"/>
       <c r="F11" s="2" t="n"/>
-      <c r="G11" s="4" t="n"/>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>UNIQUE uk_active_slot</t>
+        </is>
+      </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>拒绝理由</t>
+          <t>时段占位键</t>
         </is>
       </c>
       <c r="I11" s="4" t="n"/>
       <c r="J11" s="4" t="n"/>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>textarea</t>
+          <t>input</t>
         </is>
       </c>
       <c r="L11" s="4" t="n"/>
       <c r="M11" s="2" t="n"/>
-      <c r="N11" s="4" t="n"/>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>值形如 house_id:appointment_time，仅待确认/已确认非空，终态置 NULL 释放时段</t>
+        </is>
+      </c>
       <c r="O11" s="4" t="n"/>
       <c r="P11" s="4" t="n"/>
     </row>
@@ -11438,7 +11442,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>remark</t>
+          <t>reject_reason</t>
         </is>
       </c>
       <c r="E12" s="2" t="n"/>
@@ -11446,14 +11450,14 @@
       <c r="G12" s="4" t="n"/>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>租客留言</t>
+          <t>拒绝理由</t>
         </is>
       </c>
       <c r="I12" s="4" t="n"/>
       <c r="J12" s="4" t="n"/>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>input</t>
+          <t>textarea</t>
         </is>
       </c>
       <c r="L12" s="4" t="n"/>
@@ -11465,44 +11469,34 @@
     <row r="13">
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>DATETIME</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n"/>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>200</v>
+      </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>created_at</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
+          <t>remark</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
       <c r="G13" s="4" t="n"/>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>创建时间</t>
+          <t>租客留言</t>
         </is>
       </c>
       <c r="I13" s="4" t="n"/>
       <c r="J13" s="4" t="n"/>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>datetime</t>
+          <t>input</t>
         </is>
       </c>
       <c r="L13" s="4" t="n"/>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="M13" s="2" t="n"/>
       <c r="N13" s="4" t="n"/>
       <c r="O13" s="4" t="n"/>
       <c r="P13" s="4" t="n"/>
@@ -11516,7 +11510,7 @@
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>updated_at</t>
+          <t>created_at</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -11529,14 +11523,10 @@
           <t>CURRENT_TIMESTAMP</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>ON UPDATE CURRENT_TIMESTAMP</t>
-        </is>
-      </c>
+      <c r="G14" s="4" t="n"/>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>更新时间</t>
+          <t>创建时间</t>
         </is>
       </c>
       <c r="I14" s="4" t="n"/>
@@ -11547,13 +11537,62 @@
         </is>
       </c>
       <c r="L14" s="4" t="n"/>
-      <c r="M14" s="2" t="n"/>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="N14" s="4" t="n"/>
       <c r="O14" s="4" t="n"/>
       <c r="P14" s="4" t="n"/>
     </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>ON UPDATE CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>更新时间</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="n"/>
+      <c r="J15" s="4" t="n"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="n"/>
+      <c r="M15" s="2" t="n"/>
+      <c r="N15" s="4" t="n"/>
+      <c r="O15" s="4" t="n"/>
+      <c r="P15" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>END</t>
         </is>

--- a/doc/03.概要设计/数据库表.xlsx
+++ b/doc/03.概要设计/数据库表.xlsx
@@ -26,10 +26,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ai_analysis" sheetId="17" state="visible" r:id="rId17"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kb_document" sheetId="18" state="visible" r:id="rId18"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kb_chunk" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ai_provider_config" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'表清单'!$1:$1</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'表清单'!$A$1:$I$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'表清单'!$A$1:$I$22</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'sys_user'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'sys_user'!$A$1:$P$19</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'realname_auth'!$4:$4</definedName>
@@ -66,6 +67,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="17">'kb_document'!$A$1:$P$16</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="18">'kb_chunk'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="18">'kb_chunk'!$A$1:$P$14</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="19">'ai_provider_config'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="19">'ai_provider_config'!$A$1:$P$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -538,8 +541,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:I22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
@@ -1373,10 +1376,53 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>说明：本工作簿共 18 张业务表，与《数据库设计简介》4.3 数据字典、docker/mysql-init/01_schema.sql 三者一致；改字段请以 schema.sql 为准并同步更新本表。</t>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>ai_provider_config</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>AI API供应商配置表</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>AI 域</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>存储大语言模型（LLM）与词嵌入模型（EMBEDDING）的供应商端点、协议、凭据与参数，支持管理员控制台动态维护与热切换生效</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>说明：本工作簿共 19 张业务表，与《数据库设计简介》4.3 数据字典、docker/mysql-init/01_schema.sql 三者一致；改字段请以 schema.sql 为准并同步更新本表。</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1439,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -2099,7 +2145,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -2660,7 +2706,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -3290,7 +3336,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -3890,7 +3936,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -4410,7 +4456,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -4936,7 +4982,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -5531,7 +5577,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -6088,7 +6134,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -6653,7 +6699,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -7118,7 +7164,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -7797,14 +7843,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:P23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -7827,6 +7873,890 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
+          <t>ai_provider_config</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>表描述</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>AI API供应商配置表</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>做成日期</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1">
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>表名称</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>ai_provider_config</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="H3" s="10" t="inlineStr">
+        <is>
+          <t>存储大语言模型（LLM）与词嵌入模型（EMBEDDING）的供应商端点、协议、凭据与参数，支持管理员控制台动态维护与热切换生效</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>大小</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>非空</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>默认值</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>补充</t>
+        </is>
+      </c>
+      <c r="H4" s="1" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="I4" s="1" t="inlineStr">
+        <is>
+          <t>扩展</t>
+        </is>
+      </c>
+      <c r="J4" s="1" t="inlineStr">
+        <is>
+          <t>左</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="L4" s="1" t="inlineStr">
+        <is>
+          <t>右</t>
+        </is>
+      </c>
+      <c r="M4" s="1" t="inlineStr">
+        <is>
+          <t>List显示</t>
+        </is>
+      </c>
+      <c r="N4" s="1" t="inlineStr">
+        <is>
+          <t>特殊取值描述</t>
+        </is>
+      </c>
+      <c r="O4" s="1" t="inlineStr">
+        <is>
+          <t>追加日期</t>
+        </is>
+      </c>
+      <c r="P4" s="1" t="inlineStr">
+        <is>
+          <t>追加原因</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>BIGINT</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>主键 自增 UNSIGNED</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>主键</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="4" t="n"/>
+      <c r="M5" s="2" t="n"/>
+      <c r="N5" s="4" t="n"/>
+      <c r="O5" s="4" t="n"/>
+      <c r="P5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n"/>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>供应商名称</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
+      <c r="P6" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>idx_category_active 联合索引</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>供应商类型: LLM / EMBEDDING</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="4" t="n"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>select</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="n"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>LLM(大语言模型) / EMBEDDING(词嵌入模型)</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="n"/>
+      <c r="P7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>protocol</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>openai-chat-completions</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>接口协议</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="4" t="n"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>select</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="n"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>openai-chat-completions / anthropic-messages / openai-responses</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="n"/>
+      <c r="P8" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>255</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>base_url</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n"/>
+      <c r="G9" s="4" t="n"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>接口基址</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="n"/>
+      <c r="J9" s="4" t="n"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="n"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="n"/>
+      <c r="O9" s="4" t="n"/>
+      <c r="P9" s="4" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>255</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>api_key</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n"/>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>API Key凭据（脱敏回显）</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="n"/>
+      <c r="J10" s="4" t="n"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>password</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="n"/>
+      <c r="M10" s="2" t="n"/>
+      <c r="N10" s="4" t="n"/>
+      <c r="O10" s="4" t="n"/>
+      <c r="P10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>大模型名称</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="4" t="n"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="n"/>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n"/>
+      <c r="P11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>embedding_model</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>bge-m3</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>词嵌入模型名称</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="4" t="n"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="n"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="n"/>
+      <c r="O12" s="4" t="n"/>
+      <c r="P12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>DECIMAL</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3,2</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>temperature</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>采样温度</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="n"/>
+      <c r="J13" s="4" t="n"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="n"/>
+      <c r="M13" s="2" t="n"/>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="4" t="n"/>
+      <c r="P13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>max_tokens</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4096</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>最大Token预算</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" s="4" t="n"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="2" t="n"/>
+      <c r="N14" s="4" t="n"/>
+      <c r="O14" s="4" t="n"/>
+      <c r="P14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>INT</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>timeout_seconds</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="n"/>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>超时时间(秒)</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="n"/>
+      <c r="J15" s="4" t="n"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="n"/>
+      <c r="M15" s="2" t="n"/>
+      <c r="N15" s="4" t="n"/>
+      <c r="O15" s="4" t="n"/>
+      <c r="P15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>VARCHAR</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>255</v>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>user_agent</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>自定义User-Agent</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="n"/>
+      <c r="J16" s="4" t="n"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>input</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="n"/>
+      <c r="M16" s="2" t="n"/>
+      <c r="N16" s="4" t="n"/>
+      <c r="O16" s="4" t="n"/>
+      <c r="P16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>TEXT</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>custom_headers</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="4" t="n"/>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>自定义请求头JSON键值对</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="n"/>
+      <c r="J17" s="4" t="n"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>textarea</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="n"/>
+      <c r="M17" s="2" t="n"/>
+      <c r="N17" s="4" t="n"/>
+      <c r="O17" s="4" t="n"/>
+      <c r="P17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>TINYINT</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>is_active</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>idx_active 索引 / 业务保证同类别单激活</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>是否当前生效: 1是 0否</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4" t="n"/>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>radio</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>1:是; 0:否</t>
+        </is>
+      </c>
+      <c r="O18" s="4" t="n"/>
+      <c r="P18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>created_at</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>创建时间</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="n"/>
+      <c r="O19" s="4" t="n"/>
+      <c r="P19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>DATETIME</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>updated_at</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>ON UPDATE CURRENT_TIMESTAMP</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>更新时间</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="n"/>
+      <c r="J20" s="4" t="n"/>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>datetime</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="n"/>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="n"/>
+      <c r="O20" s="4" t="n"/>
+      <c r="P20" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>END</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="H2:N2"/>
+    <mergeCell ref="H3:N3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="C3:D3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:P17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="6" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="46" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
           <t>realname_auth</t>
         </is>
       </c>
@@ -8388,7 +9318,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -8947,7 +9877,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P32"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -10180,7 +11110,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -10620,7 +11550,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -10974,7 +11904,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -11619,7 +12549,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:P22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
